--- a/task168/golden/summer2026_upgauge_forecast.xlsx
+++ b/task168/golden/summer2026_upgauge_forecast.xlsx
@@ -973,34 +973,34 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>0.364</v>
+        <v>0.368</v>
       </c>
       <c r="H2" s="14" t="n">
-        <v>0.524</v>
+        <v>0.527</v>
       </c>
       <c r="I2" s="14" t="n">
-        <v>0.677</v>
+        <v>0.679</v>
       </c>
       <c r="J2" s="14" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="K2" s="14" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="3">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>2259</v>
+        <v>3315</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>0.005</v>
@@ -1019,22 +1019,22 @@
         <v>0.024</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>0.21</v>
+        <v>0.209</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>0.547</v>
+        <v>0.545</v>
       </c>
       <c r="I3" s="14" t="n">
         <v>0.695</v>
       </c>
       <c r="J3" s="14" t="n">
-        <v>0.858</v>
+        <v>0.857</v>
       </c>
       <c r="K3" s="14" t="n">
         <v>0.948</v>
@@ -1047,25 +1047,25 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>2204</v>
+        <v>3313</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>0.024</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.507</v>
+        <v>0.508</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>0.647</v>
+        <v>0.648</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>0.769</v>
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1891</v>
+        <v>3002</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>0.505</v>
@@ -1105,7 +1105,7 @@
         <v>0.768</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.853</v>
+        <v>0.854</v>
       </c>
       <c r="J5" s="14" t="n">
         <v>0.9360000000000001</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1658</v>
+        <v>2822</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>0.158</v>
@@ -1130,13 +1130,13 @@
         <v>0.276</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>0.581</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>0.8110000000000001</v>
@@ -1145,7 +1145,7 @@
         <v>0.882</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="K6" s="14" t="n">
         <v>0.982</v>
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1398</v>
+        <v>2555</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>0.593</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>0.8179999999999999</v>
@@ -1185,7 +1185,7 @@
         <v>0.95</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="8">
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1919</v>
+        <v>3018</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>0.207</v>
+        <v>0.209</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>0.384</v>
+        <v>0.387</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.513</v>
+        <v>0.515</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.668</v>
+        <v>0.669</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="I8" s="14" t="n">
         <v>0.855</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.977</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="9">
@@ -1232,34 +1232,34 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1889</v>
+        <v>2758</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>0.026</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>0.515</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.654</v>
+        <v>0.653</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>0.899</v>
+        <v>0.898</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="11">

--- a/task168/golden/summer2026_upgauge_forecast.xlsx
+++ b/task168/golden/summer2026_upgauge_forecast.xlsx
@@ -1579,7 +1579,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Summer 2025 departures. A passenger is turned away because the flight was full when the request was logged at or after the departure sold out. A website or app session asking again for the same departure is one party; the agency feed writes one record per passenger name; the contact centre one record per call.</t>
+          <t>Summer 2025 departures. A request was turned away because the flight was full when it was logged at or after the departure sold out (RM sell-out time). Each website or app session, call or booking reference counts once per departure, at the passengers in its request; route and direction are the departure's.</t>
         </is>
       </c>
     </row>
